--- a/data/excel/spells.xlsx
+++ b/data/excel/spells.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SunnydayBot\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906DECAC-C0E7-492E-816B-FC553CB0F2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31250CAD-84FA-474D-944B-0AB5CF67198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{53B26450-886A-4510-B449-997733B457CD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="spells" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
